--- a/Dashboard.xlsx
+++ b/Dashboard.xlsx
@@ -5,20 +5,20 @@
   <workbookPr dateCompatibility="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\OneDrive\Documentos\Projetos Dashboard\projeto-dashboard-vendas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\OneDrive\Documentos\Projetos Dashboard\dashboard-vendas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5808834F-DF42-4A01-8D14-88F7732EE704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{85A9410A-DA9A-4369-997A-D09381F9A935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-135" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{0701A71C-031F-4BBB-95D0-679F2B78E19B}"/>
+    <workbookView xWindow="-28920" yWindow="-135" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{0701A71C-031F-4BBB-95D0-679F2B78E19B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabela Dinamica" sheetId="14" r:id="rId1"/>
+    <sheet name="Tabela Dinamica" sheetId="14" state="hidden" r:id="rId1"/>
     <sheet name="Base_Dados" sheetId="1" r:id="rId2"/>
-    <sheet name="vendas_cliente" sheetId="8" r:id="rId3"/>
-    <sheet name="vendas_mes" sheetId="9" r:id="rId4"/>
-    <sheet name="vendas_produto" sheetId="11" r:id="rId5"/>
-    <sheet name="vendas_estado" sheetId="10" r:id="rId6"/>
+    <sheet name="vendas_cliente" sheetId="8" state="hidden" r:id="rId3"/>
+    <sheet name="vendas_mes" sheetId="9" state="hidden" r:id="rId4"/>
+    <sheet name="vendas_produto" sheetId="11" state="hidden" r:id="rId5"/>
+    <sheet name="vendas_estado" sheetId="10" state="hidden" r:id="rId6"/>
     <sheet name="Dashboard" sheetId="12" r:id="rId7"/>
   </sheets>
   <definedNames>
@@ -612,6 +612,15 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -623,61 +632,19 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Título 1" xfId="2" builtinId="16"/>
     <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
-  <dxfs count="228">
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
+  <dxfs count="67">
     <dxf>
       <fill>
         <patternFill>
@@ -722,59 +689,51 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89999084444715716"/>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.14999847407452621"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89999084444715716"/>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.14999847407452621"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89999084444715716"/>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.14999847407452621"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89999084444715716"/>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.14999847407452621"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89999084444715716"/>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.14999847407452621"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89999084444715716"/>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.14999847407452621"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89999084444715716"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89999084444715716"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <fill>
@@ -861,58 +820,53 @@
       </fill>
     </dxf>
     <dxf>
+      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.14999847407452621"/>
+        <patternFill>
+          <bgColor theme="3" tint="0.89999084444715716"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.14999847407452621"/>
+        <patternFill>
+          <bgColor theme="3" tint="0.89999084444715716"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.14999847407452621"/>
+        <patternFill>
+          <bgColor theme="3" tint="0.89999084444715716"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.14999847407452621"/>
+        <patternFill>
+          <bgColor theme="3" tint="0.89999084444715716"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.14999847407452621"/>
+        <patternFill>
+          <bgColor theme="3" tint="0.89999084444715716"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.14999847407452621"/>
+        <patternFill>
+          <bgColor theme="3" tint="0.89999084444715716"/>
         </patternFill>
       </fill>
     </dxf>
@@ -971,109 +925,10 @@
       <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
@@ -1115,24 +970,6 @@
       <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
     <dxf>
@@ -1152,342 +989,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1726,49 +1227,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0%">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103%"/>
-                    <a:lumMod val="102%"/>
-                    <a:tint val="94%"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50%">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110%"/>
-                    <a:lumMod val="100%"/>
-                    <a:shade val="100%"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100%">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99%"/>
-                    <a:satMod val="120%"/>
-                    <a:shade val="78%"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63%"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -2376,20 +1835,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -7496,6 +6942,138 @@
           </a:sp3d>
         </c:spPr>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="17"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="brightRoom" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="flat">
+            <a:bevelT w="50800" h="101600" prst="angle"/>
+            <a:contourClr>
+              <a:srgbClr val="000000"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="18"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="brightRoom" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="flat">
+            <a:bevelT w="50800" h="101600" prst="angle"/>
+            <a:contourClr>
+              <a:srgbClr val="000000"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="19"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="brightRoom" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="flat">
+            <a:bevelT w="50800" h="101600" prst="angle"/>
+            <a:contourClr>
+              <a:srgbClr val="000000"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="20"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="brightRoom" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="flat">
+            <a:bevelT w="50800" h="101600" prst="angle"/>
+            <a:contourClr>
+              <a:srgbClr val="000000"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="21"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="brightRoom" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="flat">
+            <a:bevelT w="50800" h="101600" prst="angle"/>
+            <a:contourClr>
+              <a:srgbClr val="000000"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="22"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:scene3d>
+            <a:camera prst="orthographicFront"/>
+            <a:lightRig rig="brightRoom" dir="t"/>
+          </a:scene3d>
+          <a:sp3d prstMaterial="flat">
+            <a:bevelT w="50800" h="101600" prst="angle"/>
+            <a:contourClr>
+              <a:srgbClr val="000000"/>
+            </a:contourClr>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -12377,7 +11955,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <mc:Fallback xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -12555,8 +12133,8 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="4" name="produto">
@@ -12579,7 +12157,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -12833,8 +12411,8 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="10" name="estado">
@@ -12857,7 +12435,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -12911,8 +12489,8 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>19051</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="11" name="Meses (data)">
@@ -12935,7 +12513,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -13884,1823 +13462,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{143A2823-6060-4E43-BE1B-2A7CC8943C24}" name="Tabela dinâmica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="42">
-  <location ref="M14:O25" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="31">
-        <item x="11"/>
-        <item x="20"/>
-        <item x="4"/>
-        <item x="27"/>
-        <item x="23"/>
-        <item x="21"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="10"/>
-        <item x="19"/>
-        <item x="22"/>
-        <item x="2"/>
-        <item x="12"/>
-        <item x="0"/>
-        <item x="18"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="24"/>
-        <item x="6"/>
-        <item x="17"/>
-        <item x="8"/>
-        <item x="15"/>
-        <item x="25"/>
-        <item x="9"/>
-        <item x="26"/>
-        <item x="16"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="31">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="19"/>
-        <item x="3"/>
-        <item x="23"/>
-        <item x="10"/>
-        <item x="24"/>
-        <item x="2"/>
-        <item x="13"/>
-        <item x="4"/>
-        <item x="28"/>
-        <item x="5"/>
-        <item x="27"/>
-        <item x="14"/>
-        <item x="20"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="17"/>
-        <item x="16"/>
-        <item x="21"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="25"/>
-        <item x="22"/>
-        <item x="29"/>
-        <item x="15"/>
-        <item x="18"/>
-        <item x="9"/>
-        <item x="26"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="11">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="9"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="5"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="369">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Soma de faturamento" fld="7" baseField="0" baseItem="0"/>
-    <dataField name="Soma de quantidade" fld="6" baseField="0" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="140">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="141">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="142">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="23" format="15" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="17" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6BA08FC9-492D-4A1E-866B-B0A9C477A4B6}" name="Tabela dinâmica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="42">
-  <location ref="B3:C11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="31">
-        <item x="11"/>
-        <item x="20"/>
-        <item x="4"/>
-        <item x="27"/>
-        <item x="23"/>
-        <item x="21"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="10"/>
-        <item x="19"/>
-        <item x="22"/>
-        <item x="2"/>
-        <item x="12"/>
-        <item x="0"/>
-        <item x="18"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="24"/>
-        <item x="6"/>
-        <item x="17"/>
-        <item x="8"/>
-        <item x="15"/>
-        <item x="25"/>
-        <item x="9"/>
-        <item x="26"/>
-        <item x="16"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="31">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="19"/>
-        <item x="3"/>
-        <item x="23"/>
-        <item x="10"/>
-        <item x="24"/>
-        <item x="2"/>
-        <item x="13"/>
-        <item x="4"/>
-        <item x="28"/>
-        <item x="5"/>
-        <item x="27"/>
-        <item x="14"/>
-        <item x="20"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="17"/>
-        <item x="16"/>
-        <item x="21"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="25"/>
-        <item x="22"/>
-        <item x="29"/>
-        <item x="15"/>
-        <item x="18"/>
-        <item x="9"/>
-        <item x="26"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="8">
-        <item x="5"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="369">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Soma de faturamento" fld="7" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="14">
-    <format dxfId="134">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="135">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="50">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="49">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="48">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="47">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="46">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="45">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="17">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="16">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="15">
-      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="14">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="13">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="12">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="10">
-    <chartFormat chart="23" format="15" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="17" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="18">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="19">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="20">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="21">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="22">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="23">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="24">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="23" format="16">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B1A38768-6731-4CE5-BE79-BB0F82175667}" name="Tabela dinâmica9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="39">
-  <location ref="P3:R20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="10">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="31">
-        <item x="11"/>
-        <item x="20"/>
-        <item x="4"/>
-        <item x="27"/>
-        <item x="23"/>
-        <item x="21"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="10"/>
-        <item x="19"/>
-        <item x="22"/>
-        <item x="2"/>
-        <item x="12"/>
-        <item x="0"/>
-        <item x="18"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="24"/>
-        <item x="6"/>
-        <item x="17"/>
-        <item x="8"/>
-        <item x="15"/>
-        <item x="25"/>
-        <item x="9"/>
-        <item x="26"/>
-        <item x="16"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="31">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="19"/>
-        <item x="3"/>
-        <item x="23"/>
-        <item x="10"/>
-        <item x="24"/>
-        <item x="2"/>
-        <item x="13"/>
-        <item x="4"/>
-        <item x="28"/>
-        <item x="5"/>
-        <item x="27"/>
-        <item x="14"/>
-        <item x="20"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="17"/>
-        <item x="16"/>
-        <item x="21"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="25"/>
-        <item x="22"/>
-        <item x="29"/>
-        <item x="15"/>
-        <item x="18"/>
-        <item x="9"/>
-        <item x="26"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="8"/>
-        <item x="2"/>
-        <item x="9"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="5"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="369">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-        <item sd="0" x="14"/>
-        <item sd="0" x="15"/>
-        <item sd="0" x="16"/>
-        <item sd="0" x="17"/>
-        <item sd="0" x="18"/>
-        <item sd="0" x="19"/>
-        <item sd="0" x="20"/>
-        <item sd="0" x="21"/>
-        <item sd="0" x="22"/>
-        <item sd="0" x="23"/>
-        <item sd="0" x="24"/>
-        <item sd="0" x="25"/>
-        <item sd="0" x="26"/>
-        <item sd="0" x="27"/>
-        <item sd="0" x="28"/>
-        <item sd="0" x="29"/>
-        <item sd="0" x="30"/>
-        <item sd="0" x="31"/>
-        <item sd="0" x="32"/>
-        <item sd="0" x="33"/>
-        <item sd="0" x="34"/>
-        <item sd="0" x="35"/>
-        <item sd="0" x="36"/>
-        <item sd="0" x="37"/>
-        <item sd="0" x="38"/>
-        <item sd="0" x="39"/>
-        <item sd="0" x="40"/>
-        <item sd="0" x="41"/>
-        <item sd="0" x="42"/>
-        <item sd="0" x="43"/>
-        <item sd="0" x="44"/>
-        <item sd="0" x="45"/>
-        <item sd="0" x="46"/>
-        <item sd="0" x="47"/>
-        <item sd="0" x="48"/>
-        <item sd="0" x="49"/>
-        <item sd="0" x="50"/>
-        <item sd="0" x="51"/>
-        <item sd="0" x="52"/>
-        <item sd="0" x="53"/>
-        <item sd="0" x="54"/>
-        <item sd="0" x="55"/>
-        <item sd="0" x="56"/>
-        <item sd="0" x="57"/>
-        <item sd="0" x="58"/>
-        <item sd="0" x="59"/>
-        <item sd="0" x="60"/>
-        <item sd="0" x="61"/>
-        <item sd="0" x="62"/>
-        <item sd="0" x="63"/>
-        <item sd="0" x="64"/>
-        <item sd="0" x="65"/>
-        <item sd="0" x="66"/>
-        <item sd="0" x="67"/>
-        <item sd="0" x="68"/>
-        <item sd="0" x="69"/>
-        <item sd="0" x="70"/>
-        <item sd="0" x="71"/>
-        <item sd="0" x="72"/>
-        <item sd="0" x="73"/>
-        <item sd="0" x="74"/>
-        <item sd="0" x="75"/>
-        <item sd="0" x="76"/>
-        <item sd="0" x="77"/>
-        <item sd="0" x="78"/>
-        <item sd="0" x="79"/>
-        <item sd="0" x="80"/>
-        <item sd="0" x="81"/>
-        <item sd="0" x="82"/>
-        <item sd="0" x="83"/>
-        <item sd="0" x="84"/>
-        <item sd="0" x="85"/>
-        <item sd="0" x="86"/>
-        <item sd="0" x="87"/>
-        <item sd="0" x="88"/>
-        <item sd="0" x="89"/>
-        <item sd="0" x="90"/>
-        <item sd="0" x="91"/>
-        <item sd="0" x="92"/>
-        <item sd="0" x="93"/>
-        <item sd="0" x="94"/>
-        <item sd="0" x="95"/>
-        <item sd="0" x="96"/>
-        <item sd="0" x="97"/>
-        <item sd="0" x="98"/>
-        <item sd="0" x="99"/>
-        <item sd="0" x="100"/>
-        <item sd="0" x="101"/>
-        <item sd="0" x="102"/>
-        <item sd="0" x="103"/>
-        <item sd="0" x="104"/>
-        <item sd="0" x="105"/>
-        <item sd="0" x="106"/>
-        <item sd="0" x="107"/>
-        <item sd="0" x="108"/>
-        <item sd="0" x="109"/>
-        <item sd="0" x="110"/>
-        <item sd="0" x="111"/>
-        <item sd="0" x="112"/>
-        <item sd="0" x="113"/>
-        <item sd="0" x="114"/>
-        <item sd="0" x="115"/>
-        <item sd="0" x="116"/>
-        <item sd="0" x="117"/>
-        <item sd="0" x="118"/>
-        <item sd="0" x="119"/>
-        <item sd="0" x="120"/>
-        <item sd="0" x="121"/>
-        <item sd="0" x="122"/>
-        <item sd="0" x="123"/>
-        <item sd="0" x="124"/>
-        <item sd="0" x="125"/>
-        <item sd="0" x="126"/>
-        <item sd="0" x="127"/>
-        <item sd="0" x="128"/>
-        <item sd="0" x="129"/>
-        <item sd="0" x="130"/>
-        <item sd="0" x="131"/>
-        <item sd="0" x="132"/>
-        <item sd="0" x="133"/>
-        <item sd="0" x="134"/>
-        <item sd="0" x="135"/>
-        <item sd="0" x="136"/>
-        <item sd="0" x="137"/>
-        <item sd="0" x="138"/>
-        <item sd="0" x="139"/>
-        <item sd="0" x="140"/>
-        <item sd="0" x="141"/>
-        <item sd="0" x="142"/>
-        <item sd="0" x="143"/>
-        <item sd="0" x="144"/>
-        <item sd="0" x="145"/>
-        <item sd="0" x="146"/>
-        <item sd="0" x="147"/>
-        <item sd="0" x="148"/>
-        <item sd="0" x="149"/>
-        <item sd="0" x="150"/>
-        <item sd="0" x="151"/>
-        <item sd="0" x="152"/>
-        <item sd="0" x="153"/>
-        <item sd="0" x="154"/>
-        <item sd="0" x="155"/>
-        <item sd="0" x="156"/>
-        <item sd="0" x="157"/>
-        <item sd="0" x="158"/>
-        <item sd="0" x="159"/>
-        <item sd="0" x="160"/>
-        <item sd="0" x="161"/>
-        <item sd="0" x="162"/>
-        <item sd="0" x="163"/>
-        <item sd="0" x="164"/>
-        <item sd="0" x="165"/>
-        <item sd="0" x="166"/>
-        <item sd="0" x="167"/>
-        <item sd="0" x="168"/>
-        <item sd="0" x="169"/>
-        <item sd="0" x="170"/>
-        <item sd="0" x="171"/>
-        <item sd="0" x="172"/>
-        <item sd="0" x="173"/>
-        <item sd="0" x="174"/>
-        <item sd="0" x="175"/>
-        <item sd="0" x="176"/>
-        <item sd="0" x="177"/>
-        <item sd="0" x="178"/>
-        <item sd="0" x="179"/>
-        <item sd="0" x="180"/>
-        <item sd="0" x="181"/>
-        <item sd="0" x="182"/>
-        <item sd="0" x="183"/>
-        <item sd="0" x="184"/>
-        <item sd="0" x="185"/>
-        <item sd="0" x="186"/>
-        <item sd="0" x="187"/>
-        <item sd="0" x="188"/>
-        <item sd="0" x="189"/>
-        <item sd="0" x="190"/>
-        <item sd="0" x="191"/>
-        <item sd="0" x="192"/>
-        <item sd="0" x="193"/>
-        <item sd="0" x="194"/>
-        <item sd="0" x="195"/>
-        <item sd="0" x="196"/>
-        <item sd="0" x="197"/>
-        <item sd="0" x="198"/>
-        <item sd="0" x="199"/>
-        <item sd="0" x="200"/>
-        <item sd="0" x="201"/>
-        <item sd="0" x="202"/>
-        <item sd="0" x="203"/>
-        <item sd="0" x="204"/>
-        <item sd="0" x="205"/>
-        <item sd="0" x="206"/>
-        <item sd="0" x="207"/>
-        <item sd="0" x="208"/>
-        <item sd="0" x="209"/>
-        <item sd="0" x="210"/>
-        <item sd="0" x="211"/>
-        <item sd="0" x="212"/>
-        <item sd="0" x="213"/>
-        <item sd="0" x="214"/>
-        <item sd="0" x="215"/>
-        <item sd="0" x="216"/>
-        <item sd="0" x="217"/>
-        <item sd="0" x="218"/>
-        <item sd="0" x="219"/>
-        <item sd="0" x="220"/>
-        <item sd="0" x="221"/>
-        <item sd="0" x="222"/>
-        <item sd="0" x="223"/>
-        <item sd="0" x="224"/>
-        <item sd="0" x="225"/>
-        <item sd="0" x="226"/>
-        <item sd="0" x="227"/>
-        <item sd="0" x="228"/>
-        <item sd="0" x="229"/>
-        <item sd="0" x="230"/>
-        <item sd="0" x="231"/>
-        <item sd="0" x="232"/>
-        <item sd="0" x="233"/>
-        <item sd="0" x="234"/>
-        <item sd="0" x="235"/>
-        <item sd="0" x="236"/>
-        <item sd="0" x="237"/>
-        <item sd="0" x="238"/>
-        <item sd="0" x="239"/>
-        <item sd="0" x="240"/>
-        <item sd="0" x="241"/>
-        <item sd="0" x="242"/>
-        <item sd="0" x="243"/>
-        <item sd="0" x="244"/>
-        <item sd="0" x="245"/>
-        <item sd="0" x="246"/>
-        <item sd="0" x="247"/>
-        <item sd="0" x="248"/>
-        <item sd="0" x="249"/>
-        <item sd="0" x="250"/>
-        <item sd="0" x="251"/>
-        <item sd="0" x="252"/>
-        <item sd="0" x="253"/>
-        <item sd="0" x="254"/>
-        <item sd="0" x="255"/>
-        <item sd="0" x="256"/>
-        <item sd="0" x="257"/>
-        <item sd="0" x="258"/>
-        <item sd="0" x="259"/>
-        <item sd="0" x="260"/>
-        <item sd="0" x="261"/>
-        <item sd="0" x="262"/>
-        <item sd="0" x="263"/>
-        <item sd="0" x="264"/>
-        <item sd="0" x="265"/>
-        <item sd="0" x="266"/>
-        <item sd="0" x="267"/>
-        <item sd="0" x="268"/>
-        <item sd="0" x="269"/>
-        <item sd="0" x="270"/>
-        <item sd="0" x="271"/>
-        <item sd="0" x="272"/>
-        <item sd="0" x="273"/>
-        <item sd="0" x="274"/>
-        <item sd="0" x="275"/>
-        <item sd="0" x="276"/>
-        <item sd="0" x="277"/>
-        <item sd="0" x="278"/>
-        <item sd="0" x="279"/>
-        <item sd="0" x="280"/>
-        <item sd="0" x="281"/>
-        <item sd="0" x="282"/>
-        <item sd="0" x="283"/>
-        <item sd="0" x="284"/>
-        <item sd="0" x="285"/>
-        <item sd="0" x="286"/>
-        <item sd="0" x="287"/>
-        <item sd="0" x="288"/>
-        <item sd="0" x="289"/>
-        <item sd="0" x="290"/>
-        <item sd="0" x="291"/>
-        <item sd="0" x="292"/>
-        <item sd="0" x="293"/>
-        <item sd="0" x="294"/>
-        <item sd="0" x="295"/>
-        <item sd="0" x="296"/>
-        <item sd="0" x="297"/>
-        <item sd="0" x="298"/>
-        <item sd="0" x="299"/>
-        <item sd="0" x="300"/>
-        <item sd="0" x="301"/>
-        <item sd="0" x="302"/>
-        <item sd="0" x="303"/>
-        <item sd="0" x="304"/>
-        <item sd="0" x="305"/>
-        <item sd="0" x="306"/>
-        <item sd="0" x="307"/>
-        <item sd="0" x="308"/>
-        <item sd="0" x="309"/>
-        <item sd="0" x="310"/>
-        <item sd="0" x="311"/>
-        <item sd="0" x="312"/>
-        <item sd="0" x="313"/>
-        <item sd="0" x="314"/>
-        <item sd="0" x="315"/>
-        <item sd="0" x="316"/>
-        <item sd="0" x="317"/>
-        <item sd="0" x="318"/>
-        <item sd="0" x="319"/>
-        <item sd="0" x="320"/>
-        <item sd="0" x="321"/>
-        <item sd="0" x="322"/>
-        <item sd="0" x="323"/>
-        <item sd="0" x="324"/>
-        <item sd="0" x="325"/>
-        <item sd="0" x="326"/>
-        <item sd="0" x="327"/>
-        <item sd="0" x="328"/>
-        <item sd="0" x="329"/>
-        <item sd="0" x="330"/>
-        <item sd="0" x="331"/>
-        <item sd="0" x="332"/>
-        <item sd="0" x="333"/>
-        <item sd="0" x="334"/>
-        <item sd="0" x="335"/>
-        <item sd="0" x="336"/>
-        <item sd="0" x="337"/>
-        <item sd="0" x="338"/>
-        <item sd="0" x="339"/>
-        <item sd="0" x="340"/>
-        <item sd="0" x="341"/>
-        <item sd="0" x="342"/>
-        <item sd="0" x="343"/>
-        <item sd="0" x="344"/>
-        <item sd="0" x="345"/>
-        <item sd="0" x="346"/>
-        <item sd="0" x="347"/>
-        <item sd="0" x="348"/>
-        <item sd="0" x="349"/>
-        <item sd="0" x="350"/>
-        <item sd="0" x="351"/>
-        <item sd="0" x="352"/>
-        <item sd="0" x="353"/>
-        <item sd="0" x="354"/>
-        <item sd="0" x="355"/>
-        <item sd="0" x="356"/>
-        <item sd="0" x="357"/>
-        <item sd="0" x="358"/>
-        <item sd="0" x="359"/>
-        <item sd="0" x="360"/>
-        <item sd="0" x="361"/>
-        <item sd="0" x="362"/>
-        <item sd="0" x="363"/>
-        <item sd="0" x="364"/>
-        <item sd="0" x="365"/>
-        <item sd="0" x="366"/>
-        <item sd="0" x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <formats count="2">
-    <format dxfId="145">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="146">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FA2D0E18-840D-419F-9783-FD73FC61AF84}" name="Tabela dinâmica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="39">
   <location ref="I17:J18" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="10">
@@ -16245,13 +14006,13 @@
     <dataField name="Soma de quantidade" fld="6" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="57">
+    <format dxfId="48">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="58">
+    <format dxfId="47">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="1">
+    <format dxfId="46">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -16293,7 +14054,706 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6BA08FC9-492D-4A1E-866B-B0A9C477A4B6}" name="Tabela dinâmica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="42">
+  <location ref="B3:C11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="31">
+        <item x="11"/>
+        <item x="20"/>
+        <item x="4"/>
+        <item x="27"/>
+        <item x="23"/>
+        <item x="21"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="10"/>
+        <item x="19"/>
+        <item x="22"/>
+        <item x="2"/>
+        <item x="12"/>
+        <item x="0"/>
+        <item x="18"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="24"/>
+        <item x="6"/>
+        <item x="17"/>
+        <item x="8"/>
+        <item x="15"/>
+        <item x="25"/>
+        <item x="9"/>
+        <item x="26"/>
+        <item x="16"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="31">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="3"/>
+        <item x="23"/>
+        <item x="10"/>
+        <item x="24"/>
+        <item x="2"/>
+        <item x="13"/>
+        <item x="4"/>
+        <item x="28"/>
+        <item x="5"/>
+        <item x="27"/>
+        <item x="14"/>
+        <item x="20"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="21"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="25"/>
+        <item x="22"/>
+        <item x="29"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="9"/>
+        <item x="26"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="5"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Soma de faturamento" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="14">
+    <format dxfId="13">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="5">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="4">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="3">
+      <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="0">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="10">
+    <chartFormat chart="23" format="15" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="17" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="18">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="19">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="20">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="21">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="22">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="23">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="24">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="23" format="16">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{117D9760-C13B-45AA-B98A-01D37F79C6F5}" name="Tabela dinâmica8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="51">
   <location ref="M3:O9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
@@ -16819,10 +15279,10 @@
     <dataField name="Soma de quantidade" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="7">
-    <format dxfId="149">
+    <format dxfId="55">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="150">
+    <format dxfId="54">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -16834,7 +15294,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="151">
+    <format dxfId="53">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -16846,7 +15306,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="152">
+    <format dxfId="52">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -16858,7 +15318,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="153">
+    <format dxfId="51">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -16870,7 +15330,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="154">
+    <format dxfId="50">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -16882,7 +15342,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="155">
+    <format dxfId="49">
       <pivotArea field="4" grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisRow" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -16951,7 +15411,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B49FD998-D494-4E96-85E2-BFBE4A64AB70}" name="Tabela dinâmica7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="44">
   <location ref="H3:I11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
@@ -17471,14 +15931,14 @@
     <dataField name="Soma de faturamento" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="136">
+    <format dxfId="57">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="137">
+    <format dxfId="56">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
-  <chartFormats count="10">
+  <chartFormats count="16">
     <chartFormat chart="23" format="15" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -17593,6 +16053,78 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="23" format="17">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="23" format="18">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="23" format="19">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="23" format="20">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="23" format="21">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="23" format="22">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -17606,7 +16138,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F6986B65-F2E5-4868-99F1-E14CE70485D7}" name="Tabela dinâmica6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="40">
   <location ref="E3:F16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
@@ -18185,10 +16717,10 @@
     <dataField name="Soma de faturamento" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="147">
+    <format dxfId="59">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="148">
+    <format dxfId="58">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -18212,6 +16744,1124 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{143A2823-6060-4E43-BE1B-2A7CC8943C24}" name="Tabela dinâmica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="42">
+  <location ref="M14:O25" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="31">
+        <item x="11"/>
+        <item x="20"/>
+        <item x="4"/>
+        <item x="27"/>
+        <item x="23"/>
+        <item x="21"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="10"/>
+        <item x="19"/>
+        <item x="22"/>
+        <item x="2"/>
+        <item x="12"/>
+        <item x="0"/>
+        <item x="18"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="24"/>
+        <item x="6"/>
+        <item x="17"/>
+        <item x="8"/>
+        <item x="15"/>
+        <item x="25"/>
+        <item x="9"/>
+        <item x="26"/>
+        <item x="16"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="31">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="3"/>
+        <item x="23"/>
+        <item x="10"/>
+        <item x="24"/>
+        <item x="2"/>
+        <item x="13"/>
+        <item x="4"/>
+        <item x="28"/>
+        <item x="5"/>
+        <item x="27"/>
+        <item x="14"/>
+        <item x="20"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="21"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="25"/>
+        <item x="22"/>
+        <item x="29"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="9"/>
+        <item x="26"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="11">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="5"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Soma de faturamento" fld="7" baseField="0" baseItem="0"/>
+    <dataField name="Soma de quantidade" fld="6" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="62">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="61">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="60">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="23" format="15" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="17" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B1A38768-6731-4CE5-BE79-BB0F82175667}" name="Tabela dinâmica9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="39">
+  <location ref="P3:R20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="31">
+        <item x="11"/>
+        <item x="20"/>
+        <item x="4"/>
+        <item x="27"/>
+        <item x="23"/>
+        <item x="21"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="10"/>
+        <item x="19"/>
+        <item x="22"/>
+        <item x="2"/>
+        <item x="12"/>
+        <item x="0"/>
+        <item x="18"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="24"/>
+        <item x="6"/>
+        <item x="17"/>
+        <item x="8"/>
+        <item x="15"/>
+        <item x="25"/>
+        <item x="9"/>
+        <item x="26"/>
+        <item x="16"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="31">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="3"/>
+        <item x="23"/>
+        <item x="10"/>
+        <item x="24"/>
+        <item x="2"/>
+        <item x="13"/>
+        <item x="4"/>
+        <item x="28"/>
+        <item x="5"/>
+        <item x="27"/>
+        <item x="14"/>
+        <item x="20"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="21"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="25"/>
+        <item x="22"/>
+        <item x="29"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="9"/>
+        <item x="26"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="8"/>
+        <item x="2"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="5"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <formats count="2">
+    <format dxfId="64">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="63">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -18737,10 +18387,10 @@
     <dataField name="Soma de faturamento" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="138">
+    <format dxfId="66">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="139">
+    <format dxfId="65">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -19424,22 +19074,22 @@
     <dataField name="Soma de faturamento" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="143">
+    <format dxfId="42">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="144">
+    <format dxfId="41">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="37">
+    <format dxfId="40">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="36">
+    <format dxfId="39">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="35">
+    <format dxfId="38">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="37">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="9" count="12">
@@ -19459,22 +19109,22 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="33">
+    <format dxfId="36">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="35">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="34">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="33">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="32">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="9" count="12">
@@ -19494,10 +19144,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="26">
+    <format dxfId="30">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="29">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -20085,13 +19735,13 @@
     <dataField name="Soma de quantidade" fld="6" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="15">
-    <format dxfId="131">
+    <format dxfId="28">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="132">
+    <format dxfId="27">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="133">
+    <format dxfId="26">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -20100,26 +19750,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="43">
+    <format dxfId="25">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="42">
+    <format dxfId="24">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="41">
+    <format dxfId="23">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="40">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="39">
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="38">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -20129,26 +19779,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="23">
+    <format dxfId="19">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="18">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="17">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="15">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -20361,12 +20011,12 @@
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{4709DA17-1F4D-47C9-BFB0-0F1E7C739915}" name="id_venda"/>
     <tableColumn id="2" xr3:uid="{1363EFF7-F9A2-42D9-8DDE-C06F4B50B609}" name="cliente"/>
-    <tableColumn id="3" xr3:uid="{71A41585-9FFF-44C2-9372-3A1DEE5C42A0}" name="data" dataDxfId="227"/>
-    <tableColumn id="4" xr3:uid="{1CD3275E-11BA-46CC-9903-FDB80B69E289}" name="preço unitário" dataDxfId="226" dataCellStyle="Vírgula"/>
+    <tableColumn id="3" xr3:uid="{71A41585-9FFF-44C2-9372-3A1DEE5C42A0}" name="data" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{1CD3275E-11BA-46CC-9903-FDB80B69E289}" name="preço unitário" dataDxfId="44" dataCellStyle="Vírgula"/>
     <tableColumn id="5" xr3:uid="{2C8FB900-C145-45A6-BB6B-CFD9E415B497}" name="produto"/>
     <tableColumn id="6" xr3:uid="{3AF5F713-D990-43B0-984B-C6DA65C9226A}" name="estado"/>
     <tableColumn id="7" xr3:uid="{34533824-852E-4EFD-81A2-327443885876}" name="quantidade"/>
-    <tableColumn id="8" xr3:uid="{DF315A16-841B-43A4-972A-D6229B94D72E}" name="faturamento" dataDxfId="225">
+    <tableColumn id="8" xr3:uid="{DF315A16-841B-43A4-972A-D6229B94D72E}" name="faturamento" dataDxfId="43">
       <calculatedColumnFormula>D2*G2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -22038,7 +21688,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A26D5AF-C7AD-4FF5-9475-67F23D172429}">
-  <dimension ref="B2:C31"/>
+  <dimension ref="A2:P31"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" customWidth="1"/>
@@ -22048,7 +21698,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="24" t="s">
         <v>47</v>
       </c>
       <c r="C2" s="2">
@@ -22056,7 +21706,7 @@
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="25" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="2">
@@ -22064,7 +21714,7 @@
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="24" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2">
@@ -22072,7 +21722,7 @@
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="25" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2">
@@ -22080,7 +21730,7 @@
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="24" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="2">
@@ -22088,7 +21738,7 @@
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="25" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="2">
@@ -22096,7 +21746,7 @@
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="24" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="2">
@@ -22104,7 +21754,7 @@
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="2">
@@ -22112,7 +21762,7 @@
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="24" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="2">
@@ -22120,7 +21770,7 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="25" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="2">
@@ -22128,7 +21778,7 @@
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="24" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="2">
@@ -22136,7 +21786,7 @@
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="2">
@@ -22144,7 +21794,7 @@
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="24" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="2">
@@ -22152,7 +21802,7 @@
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="25" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="2">
@@ -22160,7 +21810,7 @@
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="24" t="s">
         <v>18</v>
       </c>
       <c r="C16" s="2">
@@ -22168,7 +21818,7 @@
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="25" t="s">
         <v>19</v>
       </c>
       <c r="C17" s="2">
@@ -22176,7 +21826,7 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="24" t="s">
         <v>20</v>
       </c>
       <c r="C18" s="2">
@@ -22184,7 +21834,7 @@
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="25" t="s">
         <v>48</v>
       </c>
       <c r="C19" s="2">
@@ -22192,7 +21842,7 @@
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="24" t="s">
         <v>21</v>
       </c>
       <c r="C20" s="2">
@@ -22200,7 +21850,7 @@
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="25" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="2">
@@ -22208,7 +21858,7 @@
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="24" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="2">
@@ -22216,7 +21866,7 @@
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="25" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="2">
@@ -22224,7 +21874,7 @@
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="24" t="s">
         <v>25</v>
       </c>
       <c r="C24" s="2">
@@ -22232,7 +21882,7 @@
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="25" t="s">
         <v>26</v>
       </c>
       <c r="C25" s="2">
@@ -22240,7 +21890,7 @@
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="24" t="s">
         <v>27</v>
       </c>
       <c r="C26" s="2">
@@ -22248,7 +21898,7 @@
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="25" t="s">
         <v>28</v>
       </c>
       <c r="C27" s="2">
@@ -22256,7 +21906,7 @@
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="30" t="s">
+      <c r="B28" s="24" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="2">
@@ -22264,7 +21914,7 @@
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="31" t="s">
+      <c r="B29" s="25" t="s">
         <v>30</v>
       </c>
       <c r="C29" s="2">
@@ -22272,7 +21922,7 @@
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="30" t="s">
+      <c r="B30" s="24" t="s">
         <v>49</v>
       </c>
       <c r="C30" s="2">
@@ -22280,7 +21930,7 @@
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="31" t="s">
+      <c r="B31" s="25" t="s">
         <v>31</v>
       </c>
       <c r="C31" s="2">
@@ -22313,516 +21963,516 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="33"/>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
+      <c r="A1" s="26"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="33"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="33"/>
-      <c r="B3" s="33" t="s">
+      <c r="A3" s="26"/>
+      <c r="B3" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="33"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="33"/>
-      <c r="B4" s="35" t="s">
+      <c r="A4" s="26"/>
+      <c r="B4" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="27">
         <v>5100</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="33"/>
-      <c r="B5" s="35" t="s">
+      <c r="A5" s="26"/>
+      <c r="B5" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="27">
         <v>5190</v>
       </c>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="26"/>
+      <c r="Q5" s="26"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="33"/>
-      <c r="B6" s="35" t="s">
+      <c r="A6" s="26"/>
+      <c r="B6" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="27">
         <v>4800</v>
       </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="26"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="33"/>
-      <c r="B7" s="35" t="s">
+      <c r="A7" s="26"/>
+      <c r="B7" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="27">
         <v>3280</v>
       </c>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="33"/>
-      <c r="M7" s="33"/>
-      <c r="N7" s="33"/>
-      <c r="O7" s="33"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="33"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="33"/>
-      <c r="B8" s="35" t="s">
+      <c r="A8" s="26"/>
+      <c r="B8" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="27">
         <v>7650</v>
       </c>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="33"/>
-      <c r="B9" s="35" t="s">
+      <c r="A9" s="26"/>
+      <c r="B9" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="27">
         <v>4480</v>
       </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="33"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="33"/>
-      <c r="B10" s="35" t="s">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="27">
         <v>7200</v>
       </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
-      <c r="B11" s="35" t="s">
+      <c r="A11" s="26"/>
+      <c r="B11" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="27">
         <v>1600</v>
       </c>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="26"/>
+      <c r="Q11" s="26"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
-      <c r="B12" s="35" t="s">
+      <c r="A12" s="26"/>
+      <c r="B12" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="27">
         <v>3240</v>
       </c>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="26"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="26"/>
+      <c r="Q12" s="26"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="33"/>
-      <c r="B13" s="35" t="s">
+      <c r="A13" s="26"/>
+      <c r="B13" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="27">
         <v>6000</v>
       </c>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="26"/>
+      <c r="Q13" s="26"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="33"/>
-      <c r="B14" s="35" t="s">
+      <c r="A14" s="26"/>
+      <c r="B14" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="27">
         <v>4550</v>
       </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="26"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="33"/>
-      <c r="B15" s="35" t="s">
+      <c r="A15" s="26"/>
+      <c r="B15" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="27">
         <v>1200</v>
       </c>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="26"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
-      <c r="B16" s="35" t="s">
+      <c r="A16" s="26"/>
+      <c r="B16" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="27">
         <v>54290</v>
       </c>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="26"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="33"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
+      <c r="A17" s="26"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="26"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="26"/>
+      <c r="Q17" s="26"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="33"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
+      <c r="A18" s="26"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="26"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="26"/>
+      <c r="Q18" s="26"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="33"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="33"/>
-      <c r="O19" s="33"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="33"/>
+      <c r="A19" s="26"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="26"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="26"/>
+      <c r="Q19" s="26"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="33"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="33"/>
-      <c r="O20" s="33"/>
-      <c r="P20" s="33"/>
-      <c r="Q20" s="33"/>
+      <c r="A20" s="26"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="26"/>
+      <c r="Q20" s="26"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="33"/>
-      <c r="B21" s="33"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="33"/>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="33"/>
+      <c r="A21" s="26"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="26"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="26"/>
+      <c r="Q21" s="26"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="33"/>
-      <c r="B22" s="33"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="33"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="33"/>
-      <c r="Q22" s="33"/>
+      <c r="A22" s="26"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="33"/>
-      <c r="B23" s="33"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="33"/>
-      <c r="N23" s="33"/>
-      <c r="O23" s="33"/>
-      <c r="P23" s="33"/>
-      <c r="Q23" s="33"/>
+      <c r="A23" s="26"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="33"/>
-      <c r="B24" s="33"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="33"/>
-      <c r="Q24" s="33"/>
+      <c r="A24" s="26"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="26"/>
+      <c r="Q24" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -22844,696 +22494,696 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="33"/>
-      <c r="B1" s="33"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
+      <c r="A1" s="26"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="33"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="33"/>
-      <c r="B3" s="33"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="33"/>
-      <c r="R3" s="33"/>
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="33"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="33"/>
-      <c r="B5" s="33"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="33"/>
+      <c r="A5" s="26"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="26"/>
+      <c r="Q5" s="26"/>
+      <c r="R5" s="26"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="33"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="33"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="26"/>
+      <c r="R6" s="26"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="33"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="33"/>
-      <c r="M7" s="33"/>
-      <c r="N7" s="33"/>
-      <c r="O7" s="33"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="33"/>
-      <c r="R7" s="33"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
+      <c r="R7" s="26"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="33"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
+      <c r="A8" s="26"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="26"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="33"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="33"/>
-      <c r="R9" s="33"/>
+      <c r="A9" s="26"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="26"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="33"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="26"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
+      <c r="A11" s="26"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="26"/>
+      <c r="Q11" s="26"/>
+      <c r="R11" s="26"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="26"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="26"/>
+      <c r="Q12" s="26"/>
+      <c r="R12" s="26"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="33"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="33"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="26"/>
+      <c r="Q13" s="26"/>
+      <c r="R13" s="26"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="33"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="26"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="33"/>
-      <c r="B15" s="33" t="s">
+      <c r="A15" s="26"/>
+      <c r="B15" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="33" t="s">
+      <c r="D15" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="26"/>
+      <c r="R15" s="26"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
-      <c r="B16" s="35" t="s">
+      <c r="A16" s="26"/>
+      <c r="B16" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="27">
         <v>3050</v>
       </c>
-      <c r="D16" s="37">
+      <c r="D16" s="30">
         <v>13</v>
       </c>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="33"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="26"/>
+      <c r="R16" s="26"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A17" s="33"/>
-      <c r="B17" s="35" t="s">
+      <c r="A17" s="26"/>
+      <c r="B17" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="27">
         <v>2350</v>
       </c>
-      <c r="D17" s="37">
+      <c r="D17" s="30">
         <v>9</v>
       </c>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="33"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="26"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="26"/>
+      <c r="Q17" s="26"/>
+      <c r="R17" s="26"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" s="33"/>
-      <c r="B18" s="35" t="s">
+      <c r="A18" s="26"/>
+      <c r="B18" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="27">
         <v>4000</v>
       </c>
-      <c r="D18" s="37">
+      <c r="D18" s="30">
         <v>4</v>
       </c>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="33"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="26"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="26"/>
+      <c r="Q18" s="26"/>
+      <c r="R18" s="26"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" s="33"/>
-      <c r="B19" s="35" t="s">
+      <c r="A19" s="26"/>
+      <c r="B19" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="27">
         <v>1800</v>
       </c>
-      <c r="D19" s="37">
+      <c r="D19" s="30">
         <v>6</v>
       </c>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="33"/>
-      <c r="O19" s="33"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="33"/>
-      <c r="R19" s="33"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="26"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="26"/>
+      <c r="Q19" s="26"/>
+      <c r="R19" s="26"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" s="33"/>
-      <c r="B20" s="35" t="s">
+      <c r="A20" s="26"/>
+      <c r="B20" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="27">
         <v>4620</v>
       </c>
-      <c r="D20" s="37">
+      <c r="D20" s="30">
         <v>17</v>
       </c>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="33"/>
-      <c r="O20" s="33"/>
-      <c r="P20" s="33"/>
-      <c r="Q20" s="33"/>
-      <c r="R20" s="33"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="26"/>
+      <c r="Q20" s="26"/>
+      <c r="R20" s="26"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" s="33"/>
-      <c r="B21" s="35" t="s">
+      <c r="A21" s="26"/>
+      <c r="B21" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="27">
         <v>480</v>
       </c>
-      <c r="D21" s="37">
+      <c r="D21" s="30">
         <v>4</v>
       </c>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="33"/>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="33"/>
-      <c r="R21" s="33"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="26"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="26"/>
+      <c r="Q21" s="26"/>
+      <c r="R21" s="26"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22" s="33"/>
-      <c r="B22" s="35" t="s">
+      <c r="A22" s="26"/>
+      <c r="B22" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="27">
         <v>7300</v>
       </c>
-      <c r="D22" s="37">
+      <c r="D22" s="30">
         <v>4</v>
       </c>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="33"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="33"/>
-      <c r="Q22" s="33"/>
-      <c r="R22" s="33"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="26"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" s="33"/>
-      <c r="B23" s="35" t="s">
+      <c r="A23" s="26"/>
+      <c r="B23" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="27">
         <v>12400</v>
       </c>
-      <c r="D23" s="37">
+      <c r="D23" s="30">
         <v>11</v>
       </c>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="33"/>
-      <c r="N23" s="33"/>
-      <c r="O23" s="33"/>
-      <c r="P23" s="33"/>
-      <c r="Q23" s="33"/>
-      <c r="R23" s="33"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
+      <c r="R23" s="26"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24" s="33"/>
-      <c r="B24" s="35" t="s">
+      <c r="A24" s="26"/>
+      <c r="B24" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="27">
         <v>9000</v>
       </c>
-      <c r="D24" s="37">
+      <c r="D24" s="30">
         <v>8</v>
       </c>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="33"/>
-      <c r="Q24" s="33"/>
-      <c r="R24" s="33"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="26"/>
+      <c r="Q24" s="26"/>
+      <c r="R24" s="26"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25" s="33"/>
-      <c r="B25" s="35" t="s">
+      <c r="A25" s="26"/>
+      <c r="B25" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="34">
+      <c r="C25" s="27">
         <v>9290</v>
       </c>
-      <c r="D25" s="37">
+      <c r="D25" s="30">
         <v>30</v>
       </c>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="33"/>
-      <c r="N25" s="33"/>
-      <c r="O25" s="33"/>
-      <c r="P25" s="33"/>
-      <c r="Q25" s="33"/>
-      <c r="R25" s="33"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="26"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="26"/>
+      <c r="Q25" s="26"/>
+      <c r="R25" s="26"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A26" s="33"/>
-      <c r="B26" s="35" t="s">
+      <c r="A26" s="26"/>
+      <c r="B26" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="27">
         <v>54290</v>
       </c>
-      <c r="D26" s="37">
+      <c r="D26" s="30">
         <v>106</v>
       </c>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
-      <c r="N26" s="33"/>
-      <c r="O26" s="33"/>
-      <c r="P26" s="33"/>
-      <c r="Q26" s="33"/>
-      <c r="R26" s="33"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
+      <c r="Q26" s="26"/>
+      <c r="R26" s="26"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" s="33"/>
-      <c r="B27" s="33"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
-      <c r="N27" s="33"/>
-      <c r="O27" s="33"/>
-      <c r="P27" s="33"/>
-      <c r="Q27" s="33"/>
-      <c r="R27" s="33"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="26"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="26"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28" s="33"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33"/>
-      <c r="N28" s="33"/>
-      <c r="O28" s="33"/>
-      <c r="P28" s="33"/>
-      <c r="Q28" s="33"/>
-      <c r="R28" s="33"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
+      <c r="Q28" s="26"/>
+      <c r="R28" s="26"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29" s="33"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="33"/>
-      <c r="N29" s="33"/>
-      <c r="O29" s="33"/>
-      <c r="P29" s="33"/>
-      <c r="Q29" s="33"/>
-      <c r="R29" s="33"/>
+      <c r="A29" s="26"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="26"/>
+      <c r="O29" s="26"/>
+      <c r="P29" s="26"/>
+      <c r="Q29" s="26"/>
+      <c r="R29" s="26"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" s="33"/>
-      <c r="B30" s="33"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
-      <c r="L30" s="33"/>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
-      <c r="O30" s="33"/>
-      <c r="P30" s="33"/>
-      <c r="Q30" s="33"/>
-      <c r="R30" s="33"/>
+      <c r="A30" s="26"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="26"/>
+      <c r="O30" s="26"/>
+      <c r="P30" s="26"/>
+      <c r="Q30" s="26"/>
+      <c r="R30" s="26"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" s="33"/>
-      <c r="B31" s="33"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="33"/>
-      <c r="L31" s="33"/>
-      <c r="M31" s="33"/>
-      <c r="N31" s="33"/>
-      <c r="O31" s="33"/>
-      <c r="P31" s="33"/>
-      <c r="Q31" s="33"/>
-      <c r="R31" s="33"/>
+      <c r="A31" s="26"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="26"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="26"/>
+      <c r="Q31" s="26"/>
+      <c r="R31" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -23558,684 +23208,684 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="33"/>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
+      <c r="A1" s="26"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="33"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="33"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="33"/>
-      <c r="B3" s="33" t="s">
+      <c r="A3" s="26"/>
+      <c r="B3" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="33"/>
-      <c r="R3" s="33"/>
-      <c r="S3" s="33"/>
-      <c r="T3" s="33"/>
-      <c r="U3" s="33"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="33"/>
-      <c r="B4" s="35" t="s">
+      <c r="A4" s="26"/>
+      <c r="B4" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="27">
         <v>5900</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
+      <c r="S4" s="26"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="26"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="33"/>
-      <c r="B5" s="35" t="s">
+      <c r="A5" s="26"/>
+      <c r="B5" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="27">
         <v>8430</v>
       </c>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="33"/>
-      <c r="S5" s="33"/>
-      <c r="T5" s="33"/>
-      <c r="U5" s="33"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="26"/>
+      <c r="Q5" s="26"/>
+      <c r="R5" s="26"/>
+      <c r="S5" s="26"/>
+      <c r="T5" s="26"/>
+      <c r="U5" s="26"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="33"/>
-      <c r="B6" s="35" t="s">
+      <c r="A6" s="26"/>
+      <c r="B6" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="27">
         <v>14100</v>
       </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="33"/>
-      <c r="S6" s="33"/>
-      <c r="T6" s="33"/>
-      <c r="U6" s="33"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="26"/>
+      <c r="R6" s="26"/>
+      <c r="S6" s="26"/>
+      <c r="T6" s="26"/>
+      <c r="U6" s="26"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="33"/>
-      <c r="B7" s="35" t="s">
+      <c r="A7" s="26"/>
+      <c r="B7" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="27">
         <v>4150</v>
       </c>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="33"/>
-      <c r="M7" s="33"/>
-      <c r="N7" s="33"/>
-      <c r="O7" s="33"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="33"/>
-      <c r="R7" s="33"/>
-      <c r="S7" s="33"/>
-      <c r="T7" s="33"/>
-      <c r="U7" s="33"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
+      <c r="R7" s="26"/>
+      <c r="S7" s="26"/>
+      <c r="T7" s="26"/>
+      <c r="U7" s="26"/>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="33"/>
-      <c r="B8" s="35" t="s">
+      <c r="A8" s="26"/>
+      <c r="B8" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="27">
         <v>7790</v>
       </c>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="33"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="33"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="26"/>
+      <c r="S8" s="26"/>
+      <c r="T8" s="26"/>
+      <c r="U8" s="26"/>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="33"/>
-      <c r="B9" s="35" t="s">
+      <c r="A9" s="26"/>
+      <c r="B9" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="27">
         <v>6020</v>
       </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="33"/>
-      <c r="R9" s="33"/>
-      <c r="S9" s="33"/>
-      <c r="T9" s="33"/>
-      <c r="U9" s="33"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="26"/>
+      <c r="S9" s="26"/>
+      <c r="T9" s="26"/>
+      <c r="U9" s="26"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="33"/>
-      <c r="B10" s="35" t="s">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="27">
         <v>7900</v>
       </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="33"/>
-      <c r="U10" s="33"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="26"/>
+      <c r="S10" s="26"/>
+      <c r="T10" s="26"/>
+      <c r="U10" s="26"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
-      <c r="B11" s="35" t="s">
+      <c r="A11" s="26"/>
+      <c r="B11" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="27">
         <v>54290</v>
       </c>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
-      <c r="S11" s="33"/>
-      <c r="T11" s="33"/>
-      <c r="U11" s="33"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="26"/>
+      <c r="Q11" s="26"/>
+      <c r="R11" s="26"/>
+      <c r="S11" s="26"/>
+      <c r="T11" s="26"/>
+      <c r="U11" s="26"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33"/>
-      <c r="S12" s="33"/>
-      <c r="T12" s="33"/>
-      <c r="U12" s="33"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="26"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="26"/>
+      <c r="Q12" s="26"/>
+      <c r="R12" s="26"/>
+      <c r="S12" s="26"/>
+      <c r="T12" s="26"/>
+      <c r="U12" s="26"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="33"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="33"/>
-      <c r="S13" s="33"/>
-      <c r="T13" s="33"/>
-      <c r="U13" s="33"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="26"/>
+      <c r="Q13" s="26"/>
+      <c r="R13" s="26"/>
+      <c r="S13" s="26"/>
+      <c r="T13" s="26"/>
+      <c r="U13" s="26"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="33"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33"/>
-      <c r="S14" s="33"/>
-      <c r="T14" s="33"/>
-      <c r="U14" s="33"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="26"/>
+      <c r="S14" s="26"/>
+      <c r="T14" s="26"/>
+      <c r="U14" s="26"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="33"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="33"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="33"/>
+      <c r="A15" s="26"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="26"/>
+      <c r="R15" s="26"/>
+      <c r="S15" s="26"/>
+      <c r="T15" s="26"/>
+      <c r="U15" s="26"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="33"/>
-      <c r="T16" s="33"/>
-      <c r="U16" s="33"/>
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="26"/>
+      <c r="R16" s="26"/>
+      <c r="S16" s="26"/>
+      <c r="T16" s="26"/>
+      <c r="U16" s="26"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" s="33"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="33"/>
-      <c r="T17" s="33"/>
-      <c r="U17" s="33"/>
+      <c r="A17" s="26"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="26"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="26"/>
+      <c r="Q17" s="26"/>
+      <c r="R17" s="26"/>
+      <c r="S17" s="26"/>
+      <c r="T17" s="26"/>
+      <c r="U17" s="26"/>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" s="33"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="33"/>
-      <c r="T18" s="33"/>
-      <c r="U18" s="33"/>
+      <c r="A18" s="26"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="26"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="26"/>
+      <c r="Q18" s="26"/>
+      <c r="R18" s="26"/>
+      <c r="S18" s="26"/>
+      <c r="T18" s="26"/>
+      <c r="U18" s="26"/>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" s="33"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="33"/>
-      <c r="O19" s="33"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="33"/>
-      <c r="R19" s="33"/>
-      <c r="S19" s="33"/>
-      <c r="T19" s="33"/>
-      <c r="U19" s="33"/>
+      <c r="A19" s="26"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="26"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="26"/>
+      <c r="Q19" s="26"/>
+      <c r="R19" s="26"/>
+      <c r="S19" s="26"/>
+      <c r="T19" s="26"/>
+      <c r="U19" s="26"/>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" s="33"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="33"/>
-      <c r="O20" s="33"/>
-      <c r="P20" s="33"/>
-      <c r="Q20" s="33"/>
-      <c r="R20" s="33"/>
-      <c r="S20" s="33"/>
-      <c r="T20" s="33"/>
-      <c r="U20" s="33"/>
+      <c r="A20" s="26"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="26"/>
+      <c r="Q20" s="26"/>
+      <c r="R20" s="26"/>
+      <c r="S20" s="26"/>
+      <c r="T20" s="26"/>
+      <c r="U20" s="26"/>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="33"/>
-      <c r="B21" s="33"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="33"/>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="33"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="33"/>
-      <c r="T21" s="33"/>
-      <c r="U21" s="33"/>
+      <c r="A21" s="26"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="26"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="26"/>
+      <c r="Q21" s="26"/>
+      <c r="R21" s="26"/>
+      <c r="S21" s="26"/>
+      <c r="T21" s="26"/>
+      <c r="U21" s="26"/>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" s="33"/>
-      <c r="B22" s="33"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="33"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="33"/>
-      <c r="Q22" s="33"/>
-      <c r="R22" s="33"/>
-      <c r="S22" s="33"/>
-      <c r="T22" s="33"/>
-      <c r="U22" s="33"/>
+      <c r="A22" s="26"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="26"/>
+      <c r="S22" s="26"/>
+      <c r="T22" s="26"/>
+      <c r="U22" s="26"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="33"/>
-      <c r="B23" s="33"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="33"/>
-      <c r="N23" s="33"/>
-      <c r="O23" s="33"/>
-      <c r="P23" s="33"/>
-      <c r="Q23" s="33"/>
-      <c r="R23" s="33"/>
-      <c r="S23" s="33"/>
-      <c r="T23" s="33"/>
-      <c r="U23" s="33"/>
+      <c r="A23" s="26"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
+      <c r="R23" s="26"/>
+      <c r="S23" s="26"/>
+      <c r="T23" s="26"/>
+      <c r="U23" s="26"/>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" s="33"/>
-      <c r="B24" s="33"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="33"/>
-      <c r="Q24" s="33"/>
-      <c r="R24" s="33"/>
-      <c r="S24" s="33"/>
-      <c r="T24" s="33"/>
-      <c r="U24" s="33"/>
+      <c r="A24" s="26"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="26"/>
+      <c r="Q24" s="26"/>
+      <c r="R24" s="26"/>
+      <c r="S24" s="26"/>
+      <c r="T24" s="26"/>
+      <c r="U24" s="26"/>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" s="33"/>
-      <c r="B25" s="33"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="33"/>
-      <c r="N25" s="33"/>
-      <c r="O25" s="33"/>
-      <c r="P25" s="33"/>
-      <c r="Q25" s="33"/>
-      <c r="R25" s="33"/>
-      <c r="S25" s="33"/>
-      <c r="T25" s="33"/>
-      <c r="U25" s="33"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="26"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="26"/>
+      <c r="Q25" s="26"/>
+      <c r="R25" s="26"/>
+      <c r="S25" s="26"/>
+      <c r="T25" s="26"/>
+      <c r="U25" s="26"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A26" s="33"/>
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
-      <c r="N26" s="33"/>
-      <c r="O26" s="33"/>
-      <c r="P26" s="33"/>
-      <c r="Q26" s="33"/>
-      <c r="R26" s="33"/>
-      <c r="S26" s="33"/>
-      <c r="T26" s="33"/>
-      <c r="U26" s="33"/>
+      <c r="A26" s="26"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
+      <c r="Q26" s="26"/>
+      <c r="R26" s="26"/>
+      <c r="S26" s="26"/>
+      <c r="T26" s="26"/>
+      <c r="U26" s="26"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" s="33"/>
-      <c r="B27" s="33"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
-      <c r="N27" s="33"/>
-      <c r="O27" s="33"/>
-      <c r="P27" s="33"/>
-      <c r="Q27" s="33"/>
-      <c r="R27" s="33"/>
-      <c r="S27" s="33"/>
-      <c r="T27" s="33"/>
-      <c r="U27" s="33"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="26"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="26"/>
+      <c r="S27" s="26"/>
+      <c r="T27" s="26"/>
+      <c r="U27" s="26"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" s="33"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33"/>
-      <c r="N28" s="33"/>
-      <c r="O28" s="33"/>
-      <c r="P28" s="33"/>
-      <c r="Q28" s="33"/>
-      <c r="R28" s="33"/>
-      <c r="S28" s="33"/>
-      <c r="T28" s="33"/>
-      <c r="U28" s="33"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
+      <c r="Q28" s="26"/>
+      <c r="R28" s="26"/>
+      <c r="S28" s="26"/>
+      <c r="T28" s="26"/>
+      <c r="U28" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -24285,30 +23935,30 @@
     </row>
     <row r="2" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="7"/>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
+      <c r="T2" s="33"/>
+      <c r="U2" s="33"/>
+      <c r="V2" s="33"/>
+      <c r="W2" s="33"/>
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
@@ -24346,11 +23996,11 @@
         <v>68</v>
       </c>
       <c r="E4" s="8"/>
-      <c r="F4" s="32" t="s">
+      <c r="F4" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
       <c r="I4" s="8" t="s">
         <v>67</v>
       </c>
@@ -25253,27 +24903,27 @@
     </row>
     <row r="40" spans="1:23" ht="21" x14ac:dyDescent="0.35">
       <c r="A40" s="7"/>
-      <c r="B40" s="29" t="s">
+      <c r="B40" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="37"/>
+      <c r="H40" s="37"/>
+      <c r="I40" s="37"/>
+      <c r="J40" s="37"/>
+      <c r="K40" s="37"/>
+      <c r="L40" s="37"/>
+      <c r="M40" s="37"/>
+      <c r="N40" s="37"/>
+      <c r="O40" s="37"/>
+      <c r="P40" s="37"/>
+      <c r="Q40" s="37"/>
+      <c r="R40" s="37"/>
+      <c r="S40" s="37"/>
+      <c r="T40" s="37"/>
       <c r="U40" s="7"/>
       <c r="V40" s="7"/>
     </row>
@@ -25304,23 +24954,23 @@
     <row r="42" spans="1:23" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A42" s="7"/>
       <c r="B42" s="10"/>
-      <c r="C42" s="27" t="s">
+      <c r="C42" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="35"/>
       <c r="G42" s="10"/>
       <c r="H42" s="10"/>
       <c r="I42" s="10"/>
-      <c r="J42" s="27" t="s">
+      <c r="J42" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="K42" s="27"/>
-      <c r="L42" s="27"/>
-      <c r="M42" s="27"/>
-      <c r="N42" s="27"/>
-      <c r="O42" s="27"/>
+      <c r="K42" s="34"/>
+      <c r="L42" s="34"/>
+      <c r="M42" s="34"/>
+      <c r="N42" s="34"/>
+      <c r="O42" s="34"/>
       <c r="P42" s="10"/>
       <c r="Q42" s="10"/>
       <c r="R42" s="10"/>
@@ -25332,25 +24982,25 @@
     <row r="43" spans="1:23" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A43" s="7"/>
       <c r="B43" s="10"/>
-      <c r="C43" s="27" t="s">
+      <c r="C43" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="35"/>
       <c r="G43" s="10"/>
       <c r="H43" s="10"/>
       <c r="I43" s="10"/>
-      <c r="J43" s="24" t="s">
+      <c r="J43" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="K43" s="24"/>
-      <c r="L43" s="24"/>
-      <c r="M43" s="24"/>
-      <c r="N43" s="24"/>
-      <c r="O43" s="24"/>
-      <c r="P43" s="24"/>
-      <c r="Q43" s="24"/>
+      <c r="K43" s="31"/>
+      <c r="L43" s="31"/>
+      <c r="M43" s="31"/>
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
       <c r="R43" s="10"/>
       <c r="S43" s="10"/>
       <c r="T43" s="10"/>
@@ -25367,15 +25017,15 @@
       <c r="G44" s="10"/>
       <c r="H44" s="10"/>
       <c r="I44" s="10"/>
-      <c r="J44" s="25" t="s">
+      <c r="J44" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="K44" s="25"/>
-      <c r="L44" s="25"/>
-      <c r="M44" s="25"/>
-      <c r="N44" s="25"/>
-      <c r="O44" s="25"/>
-      <c r="P44" s="25"/>
+      <c r="K44" s="32"/>
+      <c r="L44" s="32"/>
+      <c r="M44" s="32"/>
+      <c r="N44" s="32"/>
+      <c r="O44" s="32"/>
+      <c r="P44" s="32"/>
       <c r="Q44" s="10"/>
       <c r="R44" s="10"/>
       <c r="S44" s="10"/>
